--- a/exports/MAXHEALTH_full_report.xlsx
+++ b/exports/MAXHEALTH_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.63</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>384</v>
+        <v>375.55</v>
       </c>
       <c r="I2" t="n">
         <v>380.0858741555</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.42</v>
+        <v>-5.55</v>
       </c>
       <c r="L2" t="n">
-        <v>5.09</v>
+        <v>6.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0.25</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>2.37</v>
+        <v>2.71</v>
       </c>
       <c r="O2" t="n">
         <v>-0.75</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>6.76</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44586.38541666666</v>
+        <v>44586.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>352.4</v>
+        <v>382.95</v>
       </c>
       <c r="I3" t="n">
         <v>382.7079327986292</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>6.16</v>
+        <v>-1.97</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>3.32</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N3" t="n">
         <v>4.98</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>13.3</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44616.38541666666</v>
+        <v>44616.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>349.8</v>
+        <v>345.2</v>
       </c>
       <c r="I4" t="n">
         <v>349.1395296179871</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>29.83333333333333</v>
+        <v>30</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.66</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>10.24</v>
+        <v>10.31</v>
       </c>
       <c r="M4" t="n">
         <v>5.14</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.55</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44649.38541666666</v>
+        <v>44649.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>350.7</v>
+        <v>356</v>
       </c>
       <c r="I5" t="n">
         <v>353.9785015937002</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>32.83333333333334</v>
+        <v>33</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.59</v>
+        <v>-3.13</v>
       </c>
       <c r="L5" t="n">
         <v>10.47</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.75</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44685.38541666666</v>
+        <v>44685.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>385.05</v>
+        <v>371.85</v>
       </c>
       <c r="I6" t="n">
         <v>378.5478777913078</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>35.83333333333334</v>
+        <v>36</v>
       </c>
       <c r="K6" t="n">
-        <v>8.16</v>
+        <v>4.45</v>
       </c>
       <c r="L6" t="n">
         <v>4.49</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>12.97</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44714.38541666666</v>
+        <v>44714.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>376.3</v>
+        <v>385</v>
       </c>
       <c r="I7" t="n">
         <v>383.7203893761425</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2</v>
+        <v>-3.54</v>
       </c>
       <c r="L7" t="n">
-        <v>4.21</v>
+        <v>4.67</v>
       </c>
       <c r="M7" t="n">
         <v>2.19</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>356.5</v>
+        <v>350.15</v>
       </c>
       <c r="I8" t="n">
         <v>353.2960933653684</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.4</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>8.050000000000001</v>
+        <v>10.55</v>
       </c>
       <c r="M8" t="n">
         <v>0.6899999999999999</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.48</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44741.55208333334</v>
+        <v>44742.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>367.8</v>
+        <v>375.3</v>
       </c>
       <c r="I9" t="n">
         <v>375.1176583206922</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.04</v>
+        <v>-7.18</v>
       </c>
       <c r="L9" t="n">
         <v>7.53</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>7.45</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44764.38541666666</v>
+        <v>44764.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>359.2</v>
+        <v>354</v>
       </c>
       <c r="I10" t="n">
         <v>354.7080004962504</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.29</v>
+        <v>-5.68</v>
       </c>
       <c r="L10" t="n">
-        <v>4.88</v>
+        <v>5.78</v>
       </c>
       <c r="M10" t="n">
         <v>0.52</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>5.51</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44776.55208333334</v>
+        <v>44777.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>370</v>
+        <v>374.35</v>
       </c>
       <c r="I11" t="n">
         <v>373.503957422877</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.52</v>
+        <v>-5.75</v>
       </c>
       <c r="L11" t="n">
-        <v>5.25</v>
+        <v>8.73</v>
       </c>
       <c r="M11" t="n">
         <v>2.23</v>
       </c>
       <c r="N11" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="O11" t="n">
         <v>-3.15</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>3.59</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44784.55208333334</v>
+        <v>44785.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>370</v>
+        <v>363.15</v>
       </c>
       <c r="I12" t="n">
         <v>364.13762937729</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.16</v>
+        <v>-2.99</v>
       </c>
       <c r="L12" t="n">
-        <v>1.66</v>
+        <v>4.09</v>
       </c>
       <c r="M12" t="n">
         <v>0.05</v>
       </c>
       <c r="N12" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
         <v>2.16</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>8.33</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44789.38541666666</v>
+        <v>44789.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>380.7</v>
+        <v>404.7</v>
       </c>
       <c r="I13" t="n">
         <v>387.4302163529933</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.83</v>
+        <v>-11.44</v>
       </c>
       <c r="L13" t="n">
-        <v>10.34</v>
+        <v>11.44</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>13.82</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44830.55208333334</v>
+        <v>44831.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>420.95</v>
+        <v>406.6</v>
       </c>
       <c r="I14" t="n">
         <v>410.9181653596693</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>41</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K14" t="n">
-        <v>4.02</v>
+        <v>0.47</v>
       </c>
       <c r="L14" t="n">
         <v>9.619999999999999</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>10.36</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44862.55208333334</v>
+        <v>44865.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>429</v>
+        <v>453.95</v>
       </c>
       <c r="I15" t="n">
         <v>430.8873676903574</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.51</v>
+        <v>-11.65</v>
       </c>
       <c r="L15" t="n">
-        <v>9.15</v>
+        <v>12.35</v>
       </c>
       <c r="M15" t="n">
         <v>2.99</v>
       </c>
       <c r="N15" t="n">
-        <v>4.06</v>
+        <v>6.34</v>
       </c>
       <c r="O15" t="n">
         <v>-2.6</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>11.79</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44880.55208333334</v>
+        <v>44881.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>433.55</v>
+        <v>417.85</v>
       </c>
       <c r="I16" t="n">
         <v>425.1167731768772</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.49</v>
+        <v>-7.95</v>
       </c>
       <c r="L16" t="n">
-        <v>5.93</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M16" t="n">
         <v>0.04</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>9.74</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44895.55208333334</v>
+        <v>44896.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>449.95</v>
+        <v>453.25</v>
       </c>
       <c r="I17" t="n">
         <v>453.0392189681483</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.68</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>8.65</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="M17" t="n">
         <v>1.65</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.63</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44911.38541666666</v>
+        <v>44911.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>433</v>
+        <v>424.9</v>
       </c>
       <c r="I18" t="n">
         <v>424.9399306161254</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.47</v>
+        <v>-6.25</v>
       </c>
       <c r="L18" t="n">
         <v>7.16</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>6.77</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44924.38541666666</v>
+        <v>44924.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>443.1</v>
+        <v>453</v>
       </c>
       <c r="I19" t="n">
         <v>450.6714720897013</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.28</v>
+        <v>-6.61</v>
       </c>
       <c r="L19" t="n">
-        <v>6.1</v>
+        <v>8.26</v>
       </c>
       <c r="M19" t="n">
         <v>1.02</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>7.1</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44950.55208333334</v>
+        <v>44951.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>432.2</v>
+        <v>427.25</v>
       </c>
       <c r="I20" t="n">
         <v>429.7896966072615</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.59</v>
+        <v>-5.68</v>
       </c>
       <c r="L20" t="n">
-        <v>5.91</v>
+        <v>6.17</v>
       </c>
       <c r="M20" t="n">
         <v>0.22</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.59</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44993.55208333334</v>
+        <v>44994.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>436.5</v>
+        <v>450.9</v>
       </c>
       <c r="I21" t="n">
         <v>443.4888727499007</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.17</v>
+        <v>-5.54</v>
       </c>
       <c r="L21" t="n">
         <v>8.51</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>6.18</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45016.38541666666</v>
+        <v>45016.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>446.7</v>
+        <v>437.45</v>
       </c>
       <c r="I22" t="n">
         <v>443.065859163735</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.93</v>
+        <v>-2.98</v>
       </c>
       <c r="L22" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="M22" t="n">
         <v>1.38</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.39</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45027.38541666666</v>
+        <v>45027.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>444.9</v>
+        <v>450</v>
       </c>
       <c r="I23" t="n">
         <v>445.1532144060059</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.7</v>
+        <v>-2.87</v>
       </c>
       <c r="L23" t="n">
         <v>5.13</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>7.81</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45079.55208333334</v>
+        <v>45082.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>532.5</v>
+        <v>521.7</v>
       </c>
       <c r="I24" t="n">
         <v>521.8517269360285</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>52</v>
+        <v>54.83333333333334</v>
       </c>
       <c r="K24" t="n">
-        <v>18.33</v>
+        <v>15.93</v>
       </c>
       <c r="L24" t="n">
         <v>3.32</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>9.41</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45083.55208333334</v>
+        <v>45084.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>525.05</v>
+        <v>555.9</v>
       </c>
       <c r="I25" t="n">
         <v>552.1549752615537</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.64</v>
+        <v>-6.56</v>
       </c>
       <c r="L25" t="n">
-        <v>3.01</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="N25" t="n">
-        <v>1.1</v>
+        <v>6.85</v>
       </c>
       <c r="O25" t="n">
         <v>-2.47</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>10.59</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45138.55208333334</v>
+        <v>45139.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>592</v>
+        <v>578.5</v>
       </c>
       <c r="I26" t="n">
         <v>590.4356537954678</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K26" t="n">
-        <v>6.49</v>
+        <v>4.07</v>
       </c>
       <c r="L26" t="n">
         <v>5.21</v>
@@ -1923,7 +2234,7 @@
         <v>0.99</v>
       </c>
       <c r="N26" t="n">
-        <v>2.99</v>
+        <v>3.19</v>
       </c>
       <c r="O26" t="n">
         <v>6.85</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>6.33</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45159.55208333334</v>
+        <v>45160.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>552.05</v>
+        <v>565.65</v>
       </c>
       <c r="I27" t="n">
         <v>564.7369695377491</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K27" t="n">
-        <v>4.57</v>
+        <v>2.22</v>
       </c>
       <c r="L27" t="n">
         <v>2.84</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45184.38541666666</v>
+        <v>45184.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>585.7</v>
+        <v>567.5</v>
       </c>
       <c r="I28" t="n">
         <v>579.5973872129327</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>3.54</v>
+        <v>0.33</v>
       </c>
       <c r="L28" t="n">
         <v>3.12</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>9.24</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45198.55208333334</v>
+        <v>45202.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>567.25</v>
+        <v>599.55</v>
       </c>
       <c r="I29" t="n">
         <v>584.9468131267473</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>14</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>0.04</v>
+        <v>-5.65</v>
       </c>
       <c r="L29" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="M29" t="n">
         <v>0.87</v>
       </c>
       <c r="N29" t="n">
-        <v>2.2</v>
+        <v>4.44</v>
       </c>
       <c r="O29" t="n">
         <v>-2.63</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>10.59</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45224.55208333334</v>
+        <v>45225.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>572.9</v>
+        <v>550.65</v>
       </c>
       <c r="I30" t="n">
         <v>551.7474693677277</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.45</v>
+        <v>-8.16</v>
       </c>
       <c r="L30" t="n">
-        <v>8.41</v>
+        <v>10.16</v>
       </c>
       <c r="M30" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="N30" t="n">
-        <v>3.79</v>
+        <v>3.96</v>
       </c>
       <c r="O30" t="n">
         <v>4.44</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>8.43</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45236.38541666666</v>
+        <v>45236.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>579.5</v>
+        <v>600.95</v>
       </c>
       <c r="I31" t="n">
         <v>593.8154216967674</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.24</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>7.79</v>
+        <v>10.6</v>
       </c>
       <c r="M31" t="n">
         <v>1.56</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45278.55208333334</v>
+        <v>45279.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>682.5</v>
+        <v>667</v>
       </c>
       <c r="I32" t="n">
         <v>671.4132450106098</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>42</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K32" t="n">
-        <v>13.57</v>
+        <v>10.99</v>
       </c>
       <c r="L32" t="n">
         <v>5.15</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>7.58</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45294.55208333334</v>
+        <v>45295.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>690.8</v>
+        <v>724</v>
       </c>
       <c r="I33" t="n">
         <v>692.236553801691</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.57</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>4.15</v>
+        <v>8.69</v>
       </c>
       <c r="M33" t="n">
         <v>1.22</v>
       </c>
       <c r="N33" t="n">
-        <v>3.83</v>
+        <v>6.4</v>
       </c>
       <c r="O33" t="n">
         <v>-2.78</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45350.55208333334</v>
+        <v>45351.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>850.9</v>
+        <v>784.4</v>
       </c>
       <c r="I34" t="n">
         <v>809.5824033127448</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K34" t="n">
-        <v>17.53</v>
+        <v>8.34</v>
       </c>
       <c r="L34" t="n">
         <v>4.41</v>
@@ -2379,7 +2786,7 @@
         <v>4.76</v>
       </c>
       <c r="N34" t="n">
-        <v>4.03</v>
+        <v>7.39</v>
       </c>
       <c r="O34" t="n">
         <v>6.4</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>14.32</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45378.38541666666</v>
+        <v>45378.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>768.4</v>
+        <v>811</v>
       </c>
       <c r="I35" t="n">
         <v>788.3381018126355</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>2.04</v>
+        <v>-3.39</v>
       </c>
       <c r="L35" t="n">
         <v>9.17</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.89</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45398.55208333334</v>
+        <v>45400.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>822</v>
+        <v>785.5</v>
       </c>
       <c r="I36" t="n">
         <v>813.782415026142</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>20</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>1.36</v>
+        <v>-3.14</v>
       </c>
       <c r="L36" t="n">
         <v>5.47</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>11.21</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45408.55208333334</v>
+        <v>45411.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>799.9</v>
+        <v>825.2</v>
       </c>
       <c r="I37" t="n">
         <v>819.0879371202209</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.83</v>
+        <v>-5.05</v>
       </c>
       <c r="L37" t="n">
-        <v>5.35</v>
+        <v>5.58</v>
       </c>
       <c r="M37" t="n">
         <v>1.05</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>12.13</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45435.55208333334</v>
+        <v>45436.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>805</v>
+        <v>793</v>
       </c>
       <c r="I38" t="n">
         <v>793.1705654826389</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.45</v>
+        <v>-3.9</v>
       </c>
       <c r="L38" t="n">
         <v>7.62</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>9.33</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45447.55208333334</v>
+        <v>45448.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>786</v>
+        <v>835.9</v>
       </c>
       <c r="I39" t="n">
         <v>810.7031545101879</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K39" t="n">
-        <v>0.88</v>
+        <v>-5.41</v>
       </c>
       <c r="L39" t="n">
-        <v>3.09</v>
+        <v>5.55</v>
       </c>
       <c r="M39" t="n">
         <v>0.59</v>
       </c>
       <c r="N39" t="n">
-        <v>2.75</v>
+        <v>4.07</v>
       </c>
       <c r="O39" t="n">
         <v>-1.98</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>14.05</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45468.55208333334</v>
+        <v>45469.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>890.8</v>
+        <v>876.05</v>
       </c>
       <c r="I40" t="n">
         <v>877.4794493867363</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K40" t="n">
-        <v>6.57</v>
+        <v>4.8</v>
       </c>
       <c r="L40" t="n">
         <v>8.99</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45474.38541666666</v>
+        <v>45474.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>947</v>
+        <v>954.05</v>
       </c>
       <c r="I41" t="n">
         <v>949.5539465884634</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.1</v>
+        <v>-8.9</v>
       </c>
       <c r="L41" t="n">
-        <v>8.44</v>
+        <v>9.57</v>
       </c>
       <c r="M41" t="n">
         <v>0.32</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45509.38541666666</v>
+        <v>45509.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>879.95</v>
+        <v>868.3</v>
       </c>
       <c r="I42" t="n">
         <v>879.4446488114872</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>34.83333333333334</v>
+        <v>35</v>
       </c>
       <c r="K42" t="n">
-        <v>-7.77</v>
+        <v>-8.99</v>
       </c>
       <c r="L42" t="n">
-        <v>8.16</v>
+        <v>9.75</v>
       </c>
       <c r="M42" t="n">
         <v>2.37</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>7.16</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45539.55208333334</v>
+        <v>45540.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>878.7</v>
+        <v>896.75</v>
       </c>
       <c r="I43" t="n">
         <v>891.5614571261652</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.2</v>
+        <v>-3.28</v>
       </c>
       <c r="L43" t="n">
-        <v>3.04</v>
+        <v>5.18</v>
       </c>
       <c r="M43" t="n">
         <v>1.12</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.77</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45565.55208333334</v>
+        <v>45566.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>995</v>
+        <v>968</v>
       </c>
       <c r="I44" t="n">
         <v>969.6552176623486</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K44" t="n">
-        <v>10.96</v>
+        <v>7.95</v>
       </c>
       <c r="L44" t="n">
         <v>3.26</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>10.27</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45593.38541666666</v>
+        <v>45593.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>958.95</v>
+        <v>970</v>
       </c>
       <c r="I45" t="n">
         <v>962.2933608248436</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>0.93</v>
+        <v>-0.21</v>
       </c>
       <c r="L45" t="n">
         <v>2.14</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.89</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45609.38541666666</v>
+        <v>45609.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>1026.15</v>
+        <v>999.95</v>
       </c>
       <c r="I46" t="n">
         <v>1005.294076055327</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K46" t="n">
-        <v>5.79</v>
+        <v>3.09</v>
       </c>
       <c r="L46" t="n">
         <v>1.32</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>10.16</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45629.55208333334</v>
+        <v>45630.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1033</v>
+        <v>1052.75</v>
       </c>
       <c r="I47" t="n">
         <v>1050.120022265691</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.31</v>
+        <v>-5.28</v>
       </c>
       <c r="L47" t="n">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="M47" t="n">
         <v>4.41</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.35</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45650.38541666666</v>
+        <v>45650.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>1141.8</v>
+        <v>1137.85</v>
       </c>
       <c r="I48" t="n">
         <v>1139.140403473699</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>8.460000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="L48" t="n">
         <v>2.45</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.27</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45663.55208333334</v>
+        <v>45664.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1161.9</v>
+        <v>1192.75</v>
       </c>
       <c r="I49" t="n">
         <v>1191.844705770857</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.11</v>
+        <v>-4.82</v>
       </c>
       <c r="L49" t="n">
         <v>6.17</v>
@@ -3234,7 +3821,7 @@
         <v>0.95</v>
       </c>
       <c r="N49" t="n">
-        <v>1.9</v>
+        <v>3.71</v>
       </c>
       <c r="O49" t="n">
         <v>-0.25</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>8.02</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45667.55208333334</v>
+        <v>45670.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1149.95</v>
+        <v>1077.65</v>
       </c>
       <c r="I50" t="n">
         <v>1131.381445993602</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.59</v>
+        <v>-9.65</v>
       </c>
       <c r="L50" t="n">
-        <v>4.06</v>
+        <v>9.83</v>
       </c>
       <c r="M50" t="n">
-        <v>-0</v>
+        <v>2.4</v>
       </c>
       <c r="N50" t="n">
-        <v>4.33</v>
+        <v>5.95</v>
       </c>
       <c r="O50" t="n">
         <v>3.71</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>11.39</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45689.38541666666</v>
+        <v>45689.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>1081.1</v>
+        <v>1116.2</v>
       </c>
       <c r="I51" t="n">
         <v>1094.915952116372</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.32</v>
+        <v>-3.58</v>
       </c>
       <c r="L51" t="n">
         <v>4.62</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>9.85</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45695.55208333334</v>
+        <v>45698.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1143.55</v>
+        <v>1071.85</v>
       </c>
       <c r="I52" t="n">
         <v>1100.038883119786</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>6</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K52" t="n">
-        <v>2.45</v>
+        <v>-3.97</v>
       </c>
       <c r="L52" t="n">
-        <v>3.18</v>
+        <v>4.21</v>
       </c>
       <c r="M52" t="n">
-        <v>0.04</v>
+        <v>0.31</v>
       </c>
       <c r="N52" t="n">
-        <v>3.28</v>
+        <v>6.26</v>
       </c>
       <c r="O52" t="n">
         <v>4.61</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>12.53</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1017.5</v>
+        <v>1083.6</v>
       </c>
       <c r="I53" t="n">
         <v>1035.776946428033</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K53" t="n">
-        <v>5.07</v>
+        <v>-1.1</v>
       </c>
       <c r="L53" t="n">
         <v>6.36</v>
@@ -3462,7 +4097,7 @@
         <v>2.85</v>
       </c>
       <c r="N53" t="n">
-        <v>3.46</v>
+        <v>6.54</v>
       </c>
       <c r="O53" t="n">
         <v>-6.26</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45748.38541666666</v>
+        <v>45748.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>1086.9</v>
+        <v>1084.75</v>
       </c>
       <c r="I54" t="n">
         <v>1086.376510305031</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>0.3</v>
+        <v>0.11</v>
       </c>
       <c r="L54" t="n">
         <v>5.41</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45782.55208333334</v>
+        <v>45783.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1134</v>
+        <v>1168</v>
       </c>
       <c r="I55" t="n">
         <v>1140.089579054194</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.54</v>
+        <v>-7.67</v>
       </c>
       <c r="L55" t="n">
-        <v>6.01</v>
+        <v>7.95</v>
       </c>
       <c r="M55" t="n">
         <v>2.97</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.27</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45826.55208333334</v>
+        <v>45827.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1183.8</v>
+        <v>1153.2</v>
       </c>
       <c r="I56" t="n">
         <v>1179.012375376125</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K56" t="n">
-        <v>1.35</v>
+        <v>-1.27</v>
       </c>
       <c r="L56" t="n">
         <v>6.68</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>7.95</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45833.38541666666</v>
+        <v>45833.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>1228.2</v>
+        <v>1236.7</v>
       </c>
       <c r="I57" t="n">
         <v>1229.802796517737</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>-6.5</v>
+        <v>-7.24</v>
       </c>
       <c r="L57" t="n">
-        <v>6.66</v>
+        <v>7.78</v>
       </c>
       <c r="M57" t="n">
         <v>1.6</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>5.93</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1250.6</v>
+        <v>1218.7</v>
       </c>
       <c r="I58" t="n">
         <v>1237.768321241227</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>1.12</v>
+        <v>-1.46</v>
       </c>
       <c r="L58" t="n">
-        <v>0.71</v>
+        <v>1.54</v>
       </c>
       <c r="M58" t="n">
         <v>1.01</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.71</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45863.38541666666</v>
+        <v>45863.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>1268.2</v>
+        <v>1282</v>
       </c>
       <c r="I59" t="n">
         <v>1276.766820384177</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.06</v>
+        <v>-5.19</v>
       </c>
       <c r="L59" t="n">
         <v>5.75</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>5.47</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45894.55208333334</v>
+        <v>45895.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1219.5</v>
+        <v>1193.2</v>
       </c>
       <c r="I60" t="n">
         <v>1211.833080358212</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>31</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.88</v>
+        <v>-6.93</v>
       </c>
       <c r="L60" t="n">
-        <v>6.08</v>
+        <v>7.94</v>
       </c>
       <c r="M60" t="n">
         <v>1.98</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>6.58</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1068.5</v>
+        <v>1131.1</v>
       </c>
       <c r="I61" t="n">
         <v>1125.423396658695</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K61" t="n">
-        <v>10.45</v>
+        <v>5.2</v>
       </c>
       <c r="L61" t="n">
         <v>2.06</v>
       </c>
       <c r="M61" t="n">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="N61" t="n">
-        <v>2.67</v>
+        <v>6.41</v>
       </c>
       <c r="O61" t="n">
         <v>-2.91</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>7.99</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45960.55208333334</v>
+        <v>45961.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1175.5</v>
+        <v>1157</v>
       </c>
       <c r="I62" t="n">
         <v>1161.729500062426</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K62" t="n">
-        <v>3.93</v>
+        <v>2.29</v>
       </c>
       <c r="L62" t="n">
         <v>3.34</v>
       </c>
       <c r="M62" t="n">
-        <v>0.34</v>
+        <v>0.66</v>
       </c>
       <c r="N62" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O62" t="n">
         <v>6.41</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>4.3</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45979.55208333334</v>
+        <v>45980.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1118.6</v>
+        <v>1163.6</v>
       </c>
       <c r="I63" t="n">
         <v>1148.522326796019</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K63" t="n">
-        <v>3.32</v>
+        <v>-0.57</v>
       </c>
       <c r="L63" t="n">
         <v>1.34</v>
@@ -4032,7 +4787,7 @@
         <v>2.59</v>
       </c>
       <c r="N63" t="n">
-        <v>1.84</v>
+        <v>4.12</v>
       </c>
       <c r="O63" t="n">
         <v>-2.25</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.58</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45992.55208333334</v>
+        <v>45993.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1131.8</v>
+        <v>1115.4</v>
       </c>
       <c r="I64" t="n">
         <v>1118.984798270362</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.73</v>
+        <v>-4.14</v>
       </c>
       <c r="L64" t="n">
         <v>5.04</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>5.74</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46014.55208333334</v>
+        <v>46015.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1075</v>
+        <v>1087.9</v>
       </c>
       <c r="I65" t="n">
         <v>1083.458445177371</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K65" t="n">
-        <v>3.62</v>
+        <v>2.47</v>
       </c>
       <c r="L65" t="n">
         <v>1.6</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>5.21</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46020.55208333334</v>
+        <v>46021.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1062</v>
+        <v>1036.1</v>
       </c>
       <c r="I66" t="n">
         <v>1036.610961801203</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.38</v>
+        <v>-4.76</v>
       </c>
       <c r="L66" t="n">
-        <v>2.58</v>
+        <v>5.03</v>
       </c>
       <c r="M66" t="n">
         <v>0.09</v>
       </c>
       <c r="N66" t="n">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="O66" t="n">
         <v>0.47</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>6.15</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>958.1</v>
+        <v>1000.1</v>
       </c>
       <c r="I67" t="n">
         <v>998.9057688955938</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K67" t="n">
-        <v>7.53</v>
+        <v>3.47</v>
       </c>
       <c r="L67" t="n">
         <v>3.18</v>
       </c>
       <c r="M67" t="n">
-        <v>0.87</v>
+        <v>5.52</v>
       </c>
       <c r="N67" t="n">
-        <v>1.78</v>
+        <v>4.89</v>
       </c>
       <c r="O67" t="n">
         <v>-1.45</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1080.2</v>
+        <v>1055.8</v>
       </c>
       <c r="I68" t="n">
         <v>1061.616343558889</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K68" t="n">
-        <v>8.01</v>
+        <v>5.57</v>
       </c>
       <c r="L68" t="n">
         <v>3.54</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>5.31</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46125.55208333334</v>
+        <v>46127.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>950.4</v>
+        <v>988.8</v>
       </c>
       <c r="I69" t="n">
         <v>977.4819645731033</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K69" t="n">
-        <v>9.98</v>
+        <v>6.35</v>
       </c>
       <c r="L69" t="n">
         <v>1.14</v>
@@ -4374,7 +5201,7 @@
         <v>1.16</v>
       </c>
       <c r="N69" t="n">
-        <v>2.72</v>
+        <v>4.27</v>
       </c>
       <c r="O69" t="n">
         <v>-2.58</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>7.64</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46164.38541666666</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>1041.15</v>
+        <v>1023.05</v>
       </c>
       <c r="I70" t="n">
         <v>1038.061403414708</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>37</v>
+        <v>37.16666666666666</v>
       </c>
       <c r="K70" t="n">
-        <v>5.29</v>
+        <v>3.46</v>
       </c>
       <c r="L70" t="n">
         <v>5.45</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>7.79</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46178.55208333334</v>
+        <v>46181.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>975.55</v>
+        <v>1004.75</v>
       </c>
       <c r="I71" t="n">
         <v>995.5119328372576</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K71" t="n">
-        <v>4.64</v>
+        <v>1.79</v>
       </c>
       <c r="L71" t="n">
         <v>1.82</v>
@@ -4488,7 +5339,7 @@
         <v>0.95</v>
       </c>
       <c r="N71" t="n">
-        <v>1.57</v>
+        <v>3.33</v>
       </c>
       <c r="O71" t="n">
         <v>-6.57</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46210.55208333334</v>
+        <v>46211.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>1114.7</v>
+        <v>1094.6</v>
       </c>
       <c r="I72" t="n">
         <v>1096.950373210451</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K72" t="n">
-        <v>10.94</v>
+        <v>8.94</v>
       </c>
       <c r="L72" t="n">
         <v>4.45</v>
@@ -4545,7 +5408,7 @@
         <v>1.05</v>
       </c>
       <c r="N72" t="n">
-        <v>1.83</v>
+        <v>2.72</v>
       </c>
       <c r="O72" t="n">
         <v>3.33</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>7.54</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46232.55208333334</v>
+        <v>46233.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>1110.1</v>
+        <v>1129.5</v>
       </c>
       <c r="I73" t="n">
         <v>1118.890973952013</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.42</v>
+        <v>-3.19</v>
       </c>
       <c r="L73" t="n">
-        <v>3.42</v>
+        <v>3.77</v>
       </c>
       <c r="M73" t="n">
         <v>0.75</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>4.97</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46237.55208333334</v>
+        <v>46238.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>1089.5</v>
+        <v>1076</v>
       </c>
       <c r="I74" t="n">
         <v>1079.165375786925</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.54</v>
+        <v>-4.74</v>
       </c>
       <c r="L74" t="n">
-        <v>3.54</v>
+        <v>4.86</v>
       </c>
       <c r="M74" t="n">
         <v>-0</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>6.43</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46273.55208333334</v>
+        <v>46274.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>994.3</v>
+        <v>1036.3</v>
       </c>
       <c r="I75" t="n">
         <v>1023.413504606136</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K75" t="n">
-        <v>7.59</v>
+        <v>3.69</v>
       </c>
       <c r="L75" t="n">
         <v>2.7</v>
@@ -4716,7 +5615,7 @@
         <v>1.69</v>
       </c>
       <c r="N75" t="n">
-        <v>2.53</v>
+        <v>4.19</v>
       </c>
       <c r="O75" t="n">
         <v>-1.39</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>6.45</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46289.55208333334</v>
+        <v>46290.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>1042.8</v>
+        <v>1014.4</v>
       </c>
       <c r="I76" t="n">
         <v>1025.779606638072</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K76" t="n">
-        <v>0.63</v>
+        <v>-2.11</v>
       </c>
       <c r="L76" t="n">
         <v>4.26</v>
@@ -4773,7 +5684,7 @@
         <v>1.87</v>
       </c>
       <c r="N76" t="n">
-        <v>1.36</v>
+        <v>2.62</v>
       </c>
       <c r="O76" t="n">
         <v>4.19</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4833,6 +5756,14 @@
       <c r="Q77" t="n">
         <v>42</v>
       </c>
+      <c r="R77" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6935,7 +7866,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="6">
@@ -6945,7 +7876,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6955,7 +7886,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55.2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
@@ -6965,7 +7896,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6975,7 +7906,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.5</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="10">
@@ -6985,7 +7916,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39.4</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="11">
@@ -6995,7 +7926,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12">
@@ -7005,7 +7936,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -7015,7 +7946,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>74.7</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="14">
@@ -7025,7 +7956,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.71</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="15">
@@ -7035,7 +7966,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.78</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="16">
@@ -7045,7 +7976,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.39</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="17">
@@ -7055,7 +7986,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18.33</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="18">
@@ -7065,7 +7996,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.7</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="19">
@@ -7075,7 +8006,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.05</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="20">
@@ -7085,7 +8016,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.04</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="21">
@@ -7095,7 +8026,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.47</v>
+        <v>12.35</v>
       </c>
     </row>
     <row r="22">
@@ -7105,7 +8036,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
@@ -7115,7 +8046,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -7125,7 +8056,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="25">
@@ -7145,7 +8076,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.71</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="27">
@@ -7165,7 +8096,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
